--- a/docs/Schedule_Gantt_Chart.xlsx
+++ b/docs/Schedule_Gantt_Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\SDR\PRISM\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{A82E4286-9BBC-4E69-B8D7-6D5373ADE5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF90B5BD-7489-492F-BCB2-9BE4CC833D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1052,6 +1052,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1087,15 +1096,6 @@
     </xf>
     <xf numFmtId="166" fontId="19" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1719,29 +1719,29 @@
       <c r="E1" s="20"/>
       <c r="F1" s="21"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
       <c r="P1" s="24"/>
-      <c r="Q1" s="105">
-        <f ca="1">TODAY()</f>
+      <c r="Q1" s="108">
+        <f>DATE(2026, 5, 11)</f>
         <v>46153</v>
       </c>
-      <c r="R1" s="104"/>
-      <c r="S1" s="104"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="104"/>
-      <c r="V1" s="104"/>
-      <c r="W1" s="104"/>
-      <c r="X1" s="104"/>
-      <c r="Y1" s="104"/>
-      <c r="Z1" s="104"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
     </row>
     <row r="2" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B2" s="87" t="s">
@@ -1753,28 +1753,28 @@
       <c r="D2" s="22"/>
       <c r="E2" s="23"/>
       <c r="F2" s="22"/>
-      <c r="I2" s="106" t="s">
+      <c r="I2" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
       <c r="P2" s="24"/>
-      <c r="Q2" s="103">
+      <c r="Q2" s="106">
         <v>1</v>
       </c>
-      <c r="R2" s="104"/>
-      <c r="S2" s="104"/>
-      <c r="T2" s="104"/>
-      <c r="U2" s="104"/>
-      <c r="V2" s="104"/>
-      <c r="W2" s="104"/>
-      <c r="X2" s="104"/>
-      <c r="Y2" s="104"/>
-      <c r="Z2" s="104"/>
+      <c r="R2" s="107"/>
+      <c r="S2" s="107"/>
+      <c r="T2" s="107"/>
+      <c r="U2" s="107"/>
+      <c r="V2" s="107"/>
+      <c r="W2" s="107"/>
+      <c r="X2" s="107"/>
+      <c r="Y2" s="107"/>
+      <c r="Z2" s="107"/>
     </row>
     <row r="3" spans="1:64" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13"/>
@@ -1790,558 +1790,558 @@
         <v>13</v>
       </c>
       <c r="E4" s="30"/>
-      <c r="I4" s="110">
-        <f ca="1">I5</f>
+      <c r="I4" s="113">
+        <f>I5</f>
         <v>46153</v>
       </c>
-      <c r="J4" s="108"/>
-      <c r="K4" s="108"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108">
-        <f ca="1">P5</f>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="111">
+        <f>P5</f>
         <v>46160</v>
       </c>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="108"/>
-      <c r="U4" s="108"/>
-      <c r="V4" s="108"/>
-      <c r="W4" s="108">
-        <f ca="1">W5</f>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111"/>
+      <c r="V4" s="111"/>
+      <c r="W4" s="111">
+        <f>W5</f>
         <v>46167</v>
       </c>
-      <c r="X4" s="108"/>
-      <c r="Y4" s="108"/>
-      <c r="Z4" s="108"/>
-      <c r="AA4" s="108"/>
-      <c r="AB4" s="108"/>
-      <c r="AC4" s="108"/>
-      <c r="AD4" s="108">
-        <f ca="1">AD5</f>
+      <c r="X4" s="111"/>
+      <c r="Y4" s="111"/>
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="111">
+        <f>AD5</f>
         <v>46174</v>
       </c>
-      <c r="AE4" s="108"/>
-      <c r="AF4" s="108"/>
-      <c r="AG4" s="108"/>
-      <c r="AH4" s="108"/>
-      <c r="AI4" s="108"/>
-      <c r="AJ4" s="108"/>
-      <c r="AK4" s="108">
-        <f ca="1">AK5</f>
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111">
+        <f>AK5</f>
         <v>46181</v>
       </c>
-      <c r="AL4" s="108"/>
-      <c r="AM4" s="108"/>
-      <c r="AN4" s="108"/>
-      <c r="AO4" s="108"/>
-      <c r="AP4" s="108"/>
-      <c r="AQ4" s="108"/>
-      <c r="AR4" s="108">
-        <f ca="1">AR5</f>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="111"/>
+      <c r="AQ4" s="111"/>
+      <c r="AR4" s="111">
+        <f>AR5</f>
         <v>46188</v>
       </c>
-      <c r="AS4" s="108"/>
-      <c r="AT4" s="108"/>
-      <c r="AU4" s="108"/>
-      <c r="AV4" s="108"/>
-      <c r="AW4" s="108"/>
-      <c r="AX4" s="108"/>
-      <c r="AY4" s="108">
-        <f ca="1">AY5</f>
+      <c r="AS4" s="111"/>
+      <c r="AT4" s="111"/>
+      <c r="AU4" s="111"/>
+      <c r="AV4" s="111"/>
+      <c r="AW4" s="111"/>
+      <c r="AX4" s="111"/>
+      <c r="AY4" s="111">
+        <f>AY5</f>
         <v>46195</v>
       </c>
-      <c r="AZ4" s="108"/>
-      <c r="BA4" s="108"/>
-      <c r="BB4" s="108"/>
-      <c r="BC4" s="108"/>
-      <c r="BD4" s="108"/>
-      <c r="BE4" s="108"/>
-      <c r="BF4" s="108">
-        <f ca="1">BF5</f>
+      <c r="AZ4" s="111"/>
+      <c r="BA4" s="111"/>
+      <c r="BB4" s="111"/>
+      <c r="BC4" s="111"/>
+      <c r="BD4" s="111"/>
+      <c r="BE4" s="111"/>
+      <c r="BF4" s="111">
+        <f>BF5</f>
         <v>46202</v>
       </c>
-      <c r="BG4" s="108"/>
-      <c r="BH4" s="108"/>
-      <c r="BI4" s="108"/>
-      <c r="BJ4" s="108"/>
-      <c r="BK4" s="108"/>
-      <c r="BL4" s="109"/>
+      <c r="BG4" s="111"/>
+      <c r="BH4" s="111"/>
+      <c r="BI4" s="111"/>
+      <c r="BJ4" s="111"/>
+      <c r="BK4" s="111"/>
+      <c r="BL4" s="112"/>
     </row>
     <row r="5" spans="1:64" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="97"/>
-      <c r="B5" s="98" t="s">
+      <c r="A5" s="100"/>
+      <c r="B5" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="100" t="s">
+      <c r="C5" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="102" t="s">
+      <c r="D5" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="102" t="s">
+      <c r="E5" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="102" t="s">
+      <c r="F5" s="105" t="s">
         <v>4</v>
       </c>
       <c r="I5" s="31">
-        <f ca="1">Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
+        <f>Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
         <v>46153</v>
       </c>
       <c r="J5" s="31">
-        <f ca="1">I5+1</f>
+        <f>I5+1</f>
         <v>46154</v>
       </c>
       <c r="K5" s="31">
-        <f t="shared" ref="K5:AX5" ca="1" si="0">J5+1</f>
+        <f t="shared" ref="K5:AX5" si="0">J5+1</f>
         <v>46155</v>
       </c>
       <c r="L5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46156</v>
       </c>
       <c r="M5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46157</v>
       </c>
       <c r="N5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46158</v>
       </c>
       <c r="O5" s="32">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46159</v>
       </c>
       <c r="P5" s="33">
-        <f ca="1">O5+1</f>
+        <f>O5+1</f>
         <v>46160</v>
       </c>
       <c r="Q5" s="31">
-        <f ca="1">P5+1</f>
+        <f>P5+1</f>
         <v>46161</v>
       </c>
       <c r="R5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46162</v>
       </c>
       <c r="S5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46163</v>
       </c>
       <c r="T5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46164</v>
       </c>
       <c r="U5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46165</v>
       </c>
       <c r="V5" s="32">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46166</v>
       </c>
       <c r="W5" s="33">
-        <f ca="1">V5+1</f>
+        <f>V5+1</f>
         <v>46167</v>
       </c>
       <c r="X5" s="31">
-        <f ca="1">W5+1</f>
+        <f>W5+1</f>
         <v>46168</v>
       </c>
       <c r="Y5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46169</v>
       </c>
       <c r="Z5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46170</v>
       </c>
       <c r="AA5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46171</v>
       </c>
       <c r="AB5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46172</v>
       </c>
       <c r="AC5" s="32">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46173</v>
       </c>
       <c r="AD5" s="33">
-        <f ca="1">AC5+1</f>
+        <f>AC5+1</f>
         <v>46174</v>
       </c>
       <c r="AE5" s="31">
-        <f ca="1">AD5+1</f>
+        <f>AD5+1</f>
         <v>46175</v>
       </c>
       <c r="AF5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46176</v>
       </c>
       <c r="AG5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46177</v>
       </c>
       <c r="AH5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46178</v>
       </c>
       <c r="AI5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46179</v>
       </c>
       <c r="AJ5" s="32">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46180</v>
       </c>
       <c r="AK5" s="33">
-        <f ca="1">AJ5+1</f>
+        <f>AJ5+1</f>
         <v>46181</v>
       </c>
       <c r="AL5" s="31">
-        <f ca="1">AK5+1</f>
+        <f>AK5+1</f>
         <v>46182</v>
       </c>
       <c r="AM5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46183</v>
       </c>
       <c r="AN5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46184</v>
       </c>
       <c r="AO5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="AP5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46186</v>
       </c>
       <c r="AQ5" s="32">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46187</v>
       </c>
       <c r="AR5" s="33">
-        <f ca="1">AQ5+1</f>
+        <f>AQ5+1</f>
         <v>46188</v>
       </c>
       <c r="AS5" s="31">
-        <f ca="1">AR5+1</f>
+        <f>AR5+1</f>
         <v>46189</v>
       </c>
       <c r="AT5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46190</v>
       </c>
       <c r="AU5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46191</v>
       </c>
       <c r="AV5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46192</v>
       </c>
       <c r="AW5" s="31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46193</v>
       </c>
       <c r="AX5" s="32">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>46194</v>
       </c>
       <c r="AY5" s="33">
-        <f ca="1">AX5+1</f>
+        <f>AX5+1</f>
         <v>46195</v>
       </c>
       <c r="AZ5" s="31">
-        <f ca="1">AY5+1</f>
+        <f>AY5+1</f>
         <v>46196</v>
       </c>
       <c r="BA5" s="31">
-        <f t="shared" ref="BA5:BE5" ca="1" si="1">AZ5+1</f>
+        <f t="shared" ref="BA5:BE5" si="1">AZ5+1</f>
         <v>46197</v>
       </c>
       <c r="BB5" s="31">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>46198</v>
       </c>
       <c r="BC5" s="31">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>46199</v>
       </c>
       <c r="BD5" s="31">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>46200</v>
       </c>
       <c r="BE5" s="32">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>46201</v>
       </c>
       <c r="BF5" s="33">
-        <f ca="1">BE5+1</f>
+        <f>BE5+1</f>
         <v>46202</v>
       </c>
       <c r="BG5" s="31">
-        <f ca="1">BF5+1</f>
+        <f>BF5+1</f>
         <v>46203</v>
       </c>
       <c r="BH5" s="31">
-        <f t="shared" ref="BH5:BL5" ca="1" si="2">BG5+1</f>
+        <f t="shared" ref="BH5:BL5" si="2">BG5+1</f>
         <v>46204</v>
       </c>
       <c r="BI5" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>46205</v>
       </c>
       <c r="BJ5" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>46206</v>
       </c>
       <c r="BK5" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>46207</v>
       </c>
       <c r="BL5" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>46208</v>
       </c>
     </row>
     <row r="6" spans="1:64" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="97"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
+      <c r="A6" s="100"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
       <c r="I6" s="34" t="str">
-        <f t="shared" ref="I6:AN6" ca="1" si="3">LEFT(TEXT(I5,"ddd"),1)</f>
+        <f t="shared" ref="I6:AN6" si="3">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
       </c>
       <c r="J6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="K6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>W</v>
       </c>
       <c r="L6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="M6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="N6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="O6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="P6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="Q6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="R6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>W</v>
       </c>
       <c r="S6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="T6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="U6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="V6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="W6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="X6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="Y6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>W</v>
       </c>
       <c r="Z6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="AA6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="AB6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AC6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AD6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="AE6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="AF6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>W</v>
       </c>
       <c r="AG6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="AH6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="AI6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AJ6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AK6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="AL6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="AM6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>W</v>
       </c>
       <c r="AN6" s="35" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="AO6" s="35" t="str">
-        <f t="shared" ref="AO6:BL6" ca="1" si="4">LEFT(TEXT(AO5,"ddd"),1)</f>
+        <f t="shared" ref="AO6:BL6" si="4">LEFT(TEXT(AO5,"ddd"),1)</f>
         <v>F</v>
       </c>
       <c r="AP6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="AQ6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="AR6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
       <c r="AS6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>T</v>
       </c>
       <c r="AT6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>W</v>
       </c>
       <c r="AU6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>T</v>
       </c>
       <c r="AV6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>F</v>
       </c>
       <c r="AW6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="AX6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="AY6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
       <c r="AZ6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>T</v>
       </c>
       <c r="BA6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>W</v>
       </c>
       <c r="BB6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>T</v>
       </c>
       <c r="BC6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>F</v>
       </c>
       <c r="BD6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="BE6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="BF6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
       <c r="BG6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>T</v>
       </c>
       <c r="BH6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>W</v>
       </c>
       <c r="BI6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>T</v>
       </c>
       <c r="BJ6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>F</v>
       </c>
       <c r="BK6" s="35" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="BL6" s="36" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
     </row>
@@ -2498,16 +2498,16 @@
         <v>0.7</v>
       </c>
       <c r="E9" s="50">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46153</v>
       </c>
       <c r="F9" s="50">
-        <f ca="1">E9+3</f>
+        <f>E9+3</f>
         <v>46156</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I9" s="51"/>
@@ -2579,11 +2579,11 @@
         <v>1</v>
       </c>
       <c r="E10" s="50">
-        <f ca="1">E9</f>
+        <f>E9</f>
         <v>46153</v>
       </c>
       <c r="F10" s="50">
-        <f ca="1">E10+2</f>
+        <f>E10+2</f>
         <v>46155</v>
       </c>
       <c r="G10" s="17"/>
@@ -2657,16 +2657,16 @@
         <v>0.6</v>
       </c>
       <c r="E11" s="55">
-        <f ca="1">E9+1</f>
+        <f>E9+1</f>
         <v>46154</v>
       </c>
       <c r="F11" s="55">
-        <f ca="1">E11+2</f>
+        <f>E11+2</f>
         <v>46156</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I11" s="51"/>
@@ -2738,16 +2738,16 @@
         <v>1</v>
       </c>
       <c r="E12" s="55">
-        <f ca="1">F11</f>
+        <f>F11</f>
         <v>46156</v>
       </c>
       <c r="F12" s="55">
-        <f ca="1">E12+1</f>
+        <f>E12+1</f>
         <v>46157</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I12" s="51"/>
@@ -2813,9 +2813,9 @@
         <v>23</v>
       </c>
       <c r="C13" s="58"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="113"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
       <c r="G13" s="17"/>
       <c r="H13" s="5" t="str">
         <f t="shared" si="5"/>
@@ -2834,16 +2834,16 @@
         <v>0.5</v>
       </c>
       <c r="E14" s="62">
-        <f ca="1">E12+1</f>
+        <f>E12+1</f>
         <v>46157</v>
       </c>
       <c r="F14" s="62">
-        <f ca="1">E14+7</f>
+        <f>E14+7</f>
         <v>46164</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="I14" s="51"/>
@@ -2915,16 +2915,16 @@
         <v>0.75</v>
       </c>
       <c r="E15" s="62">
-        <f ca="1">E14+2</f>
+        <f>E14+2</f>
         <v>46159</v>
       </c>
       <c r="F15" s="62">
-        <f ca="1">E15+1</f>
+        <f>E15+1</f>
         <v>46160</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I15" s="51"/>
@@ -2996,16 +2996,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="62">
-        <f ca="1">F15</f>
+        <f>F15</f>
         <v>46160</v>
       </c>
       <c r="F16" s="62">
-        <f ca="1">E16+3</f>
+        <f>E16+3</f>
         <v>46163</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I16" s="51"/>
@@ -3077,16 +3077,16 @@
         <v>0.15</v>
       </c>
       <c r="E17" s="62">
-        <f ca="1">E16</f>
+        <f>E16</f>
         <v>46160</v>
       </c>
       <c r="F17" s="62">
-        <f ca="1">E17+1</f>
+        <f>E17+1</f>
         <v>46161</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I17" s="51"/>
@@ -3158,16 +3158,16 @@
         <v>0</v>
       </c>
       <c r="E18" s="62">
-        <f ca="1">E17</f>
+        <f>E17</f>
         <v>46160</v>
       </c>
       <c r="F18" s="62">
-        <f ca="1">E18+3</f>
+        <f>E18+3</f>
         <v>46163</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I18" s="51"/>
@@ -3239,16 +3239,16 @@
         <v>0</v>
       </c>
       <c r="E19" s="66">
-        <f ca="1">E18+1</f>
+        <f>E18+1</f>
         <v>46161</v>
       </c>
       <c r="F19" s="66">
-        <f ca="1">E19+14</f>
+        <f>E19+14</f>
         <v>46175</v>
       </c>
       <c r="G19" s="17"/>
       <c r="H19" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="I19" s="51"/>
@@ -3320,16 +3320,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="66">
-        <f ca="1">E19</f>
+        <f>E19</f>
         <v>46161</v>
       </c>
       <c r="F20" s="66">
-        <f ca="1">E20+4</f>
+        <f>E20+4</f>
         <v>46165</v>
       </c>
       <c r="G20" s="17"/>
       <c r="H20" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I20" s="51"/>
@@ -3401,11 +3401,11 @@
         <v>0</v>
       </c>
       <c r="E21" s="66">
-        <f ca="1">F19</f>
+        <f>F19</f>
         <v>46175</v>
       </c>
       <c r="F21" s="66">
-        <f ca="1">E21+5</f>
+        <f>E21+5</f>
         <v>46180</v>
       </c>
       <c r="G21" s="17"/>
@@ -3479,17 +3479,17 @@
         <v>0</v>
       </c>
       <c r="E22" s="66">
-        <f ca="1">F21</f>
+        <f>F21</f>
         <v>46180</v>
       </c>
       <c r="F22" s="66">
-        <f ca="1">E22+5</f>
-        <v>46185</v>
+        <f>E22+10</f>
+        <v>46190</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="5">
-        <f t="shared" ca="1" si="5"/>
-        <v>6</v>
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="I22" s="51"/>
       <c r="J22" s="51"/>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="E23" s="66">
-        <f ca="1">F22+1</f>
-        <v>46186</v>
+        <f>F22+1</f>
+        <v>46191</v>
       </c>
       <c r="F23" s="66">
-        <f ca="1">E23+4</f>
-        <v>46190</v>
+        <f>E23+4</f>
+        <v>46195</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I23" s="51"/>
@@ -3641,16 +3641,16 @@
         <v>0</v>
       </c>
       <c r="E24" s="66">
-        <f ca="1">F23</f>
-        <v>46190</v>
+        <f>F23</f>
+        <v>46195</v>
       </c>
       <c r="F24" s="66">
-        <f ca="1">E24+4</f>
-        <v>46194</v>
+        <f>E24+4</f>
+        <v>46199</v>
       </c>
       <c r="G24" s="17"/>
       <c r="H24" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I24" s="51"/>
@@ -3793,16 +3793,16 @@
         <v>0</v>
       </c>
       <c r="E26" s="76">
-        <f ca="1">E19</f>
+        <f>E19</f>
         <v>46161</v>
       </c>
       <c r="F26" s="76">
-        <f ca="1">E26+3</f>
+        <f>E26+3</f>
         <v>46164</v>
       </c>
       <c r="G26" s="17"/>
       <c r="H26" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I26" s="51"/>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="E27" s="76">
-        <f ca="1">F21</f>
+        <f>F21</f>
         <v>46180</v>
       </c>
       <c r="F27" s="76">
-        <f ca="1">E27+4</f>
+        <f>E27+4</f>
         <v>46184</v>
       </c>
       <c r="G27" s="17"/>
       <c r="H27" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I27" s="51"/>
@@ -3955,16 +3955,16 @@
         <v>0</v>
       </c>
       <c r="E28" s="76">
-        <f ca="1">F24+1</f>
-        <v>46195</v>
+        <f>F24+1</f>
+        <v>46200</v>
       </c>
       <c r="F28" s="76">
-        <f ca="1">E28+3</f>
-        <v>46198</v>
+        <f>E28+3</f>
+        <v>46203</v>
       </c>
       <c r="G28" s="17"/>
       <c r="H28" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I28" s="51"/>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="E29" s="76">
-        <f ca="1">F24</f>
-        <v>46194</v>
+        <f>F24</f>
+        <v>46199</v>
       </c>
       <c r="F29" s="76">
-        <f ca="1">E29+3</f>
-        <v>46197</v>
+        <f>E29+3</f>
+        <v>46202</v>
       </c>
       <c r="G29" s="17"/>
       <c r="H29" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I29" s="51"/>
@@ -4349,12 +4349,12 @@
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup scale="57" fitToHeight="0" orientation="landscape" r:id="rId3"/>
+  <pageSetup scale="51" fitToHeight="0" orientation="landscape" r:id="rId3"/>
   <headerFooter differentFirst="1" scaleWithDoc="0">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError sqref="F22 F27 F10 F16:F17 E19 F20 E23" formula="1"/>
+    <ignoredError sqref="F27 F10 F16:F17 E19 F20 E23" formula="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
